--- a/data/gravel/Mason Bokeh 2025.xlsx
+++ b/data/gravel/Mason Bokeh 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A199D48-9888-B84B-BBF3-F08796719BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C9BB6B-FA9D-D24E-9D07-43D75C278002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="500" windowWidth="25680" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="137">
   <si>
     <t>brand</t>
   </si>
@@ -426,6 +426,24 @@
   </si>
   <si>
     <t>Bokeh</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -807,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2297,11 +2315,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -2313,7 +2329,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2327,11 +2343,9 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="1">
-        <v>27.2</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -2343,11 +2357,9 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2359,11 +2371,9 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="1">
-        <v>42</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2375,11 +2385,9 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" s="1">
-        <v>48</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -2391,10 +2399,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B59" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -2407,11 +2415,9 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" s="1">
-        <v>160</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2423,9 +2429,11 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B61" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2437,10 +2445,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -2453,10 +2461,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>73</v>
+        <v>46</v>
+      </c>
+      <c r="B63" s="1">
+        <v>42</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -2469,9 +2477,11 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="B64" s="1">
+        <v>48</v>
+      </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2483,9 +2493,11 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B65" s="1">
+        <v>180</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2497,10 +2509,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B66" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2513,11 +2525,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2529,10 +2539,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2545,10 +2555,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -2557,14 +2567,13 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2572,14 +2581,13 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2587,13 +2595,14 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2602,13 +2611,14 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B73" s="1">
-        <v>1450</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -2617,13 +2627,14 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B74" s="1">
-        <v>2850</v>
+        <v>1</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2632,13 +2643,14 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="B75" s="1">
+        <v>3</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -2650,10 +2662,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -2664,10 +2676,100 @@
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1450</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2850</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>119</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>120</v>
       </c>
     </row>
